--- a/agent-correction-tracker.xlsx
+++ b/agent-correction-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deepamk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A48477-6DF9-6A46-ADF0-40F931014FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{206C8DBD-094B-0F49-A82B-5E1794CA11EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -64,6 +64,12 @@
     <t>Logged By</t>
   </si>
   <si>
+    <t>2026-08-01</t>
+  </si>
+  <si>
+    <t>TASK-001</t>
+  </si>
+  <si>
     <t>Test Generation</t>
   </si>
   <si>
@@ -148,6 +154,9 @@
     <t>Overview</t>
   </si>
   <si>
+    <t>Correction Category Breakdown</t>
+  </si>
+  <si>
     <t>Total tasks logged</t>
   </si>
   <si>
@@ -193,6 +202,9 @@
     <t>Rate</t>
   </si>
   <si>
+    <t>Correction Rate Trend (cumulative)</t>
+  </si>
+  <si>
     <t>Documentation</t>
   </si>
   <si>
@@ -205,6 +217,18 @@
     <t>A high correction rate on one category means tighten your task specs there, not that the agent is bad.</t>
   </si>
   <si>
+    <t>Chart data (auto, do not edit)</t>
+  </si>
+  <si>
+    <t>Task #</t>
+  </si>
+  <si>
+    <t>Cumulative Correction Rate</t>
+  </si>
+  <si>
+    <t>Corrections by Task Category</t>
+  </si>
+  <si>
     <t>Agent Correction Tracker</t>
   </si>
   <si>
@@ -278,6 +302,9 @@
   </si>
   <si>
     <t>on what kind of work.</t>
+  </si>
+  <si>
+    <t>Generated integrations test cases for the service, no changes needed</t>
   </si>
 </sst>
 </file>
@@ -287,13 +314,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -347,12 +379,26 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FF999999"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FF1F2937"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="16"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -374,7 +420,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F0FE"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFF3F4F6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F4F6"/>
+        <bgColor rgb="FFE8F0FE"/>
       </patternFill>
     </fill>
   </fills>
@@ -405,30 +457,38 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,10 +511,10 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFC0504D"/>
       <rgbColor rgb="FFFFF9C4"/>
       <rgbColor rgb="FFE8F0FE"/>
       <rgbColor rgb="FF660066"/>
@@ -470,28 +530,28 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF3F4F6"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
       <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FF4A7EBB"/>
+      <rgbColor rgb="FF4BACC6"/>
+      <rgbColor rgb="FF9BBB59"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFF79646"/>
       <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF555555"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF8064A2"/>
+      <rgbColor rgb="FF999999"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF4F81BD"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF1F2937"/>
       <rgbColor rgb="00003366"/>
       <rgbColor rgb="00339966"/>
@@ -512,6 +572,1311 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:doughnutChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="C0504D"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="9BBB59"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="8064A2"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4BACC6"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="F79646"/>
+              </a:solidFill>
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:spPr/>
+              <c:txPr>
+                <a:bodyPr wrap="square"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
+                      <a:latin typeface="Calibri"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="1"/>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="1"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator>
+</c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$12:$A$17</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Wrong Assumption</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Missed Edge Case</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Scope Creep</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Style Mismatch</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Logic Error</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Other</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$12:$B$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-1885-2D4F-94D8-BC6C29D6FB6C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Dashboard!$B$37</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Cumulative Correction Rate</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28440">
+              <a:solidFill>
+                <a:srgbClr val="4A7EBB"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Dashboard!$A$38:$A$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$38:$B$52</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.66666666666666663</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>#N/A</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-97C7-2644-9088-F753C66758BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:smooth val="0"/>
+        <c:axId val="93928920"/>
+        <c:axId val="9064647"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="93928920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Task #</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9064647"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="9064647"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Correction rate</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="93928920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="4F81BD"/>
+            </a:solidFill>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Dashboard!$A$22:$A$28</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Test Generation</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>New Feature</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Refactor</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Bug Fix</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Documentation</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Config/Boilerplate</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Other</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Dashboard!$B$22:$B$28</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-37A4-B14D-B5E5-40E186995EE6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="11523475"/>
+        <c:axId val="12731634"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="11523475"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="12731634"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="12731634"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1000" b="1" strike="noStrike" spc="-1">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:rPr>
+                  <a:t>Tasks</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="11523475"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>38880</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>38880</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>160920</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>38880</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>182880</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -693,7 +2058,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -706,348 +2071,372 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8" ht="28" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F2" s="5"/>
+      <c r="G2" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="B3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="C3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="F3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="E4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="A10" s="6"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="A18" s="6"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="A21" s="6"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>27</v>
-      </c>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" s="6"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="5" t="s">
-        <v>28</v>
+      <c r="A28" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="5" t="s">
-        <v>29</v>
+      <c r="A29" s="8" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="5" t="s">
-        <v>30</v>
+      <c r="A30" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>31</v>
+      <c r="A31" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>32</v>
+      <c r="A32" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="E2:E999" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Y,N"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F999" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Wrong Assumption,Missed Edge Case,Scope Creep,Style Mismatch,Logic Error,Other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C999" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C1000" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Test Generation,New Feature,Refactor,Bug Fix,Documentation,Config/Boilerplate,Other"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1059,286 +2448,485 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="6" width="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-    </row>
-    <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="8">
-        <f>COUNTIF(Log!B2:B199,"?*")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="8">
-        <f>COUNTIFS(Log!B2:B199,"?*",Log!E2:E199,"Y")</f>
+      <c r="G4" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="11">
+        <f>COUNTIF(Log!B2:B200,"?*")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="11">
+        <f>COUNTIFS(Log!B2:B200,"?*",Log!E2:E200,"Y")</f>
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="9">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="12">
         <f>IFERROR(B6/B5,"—")</f>
-        <v>0.66666666666666663</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="11" t="s">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="14">
+        <f>COUNTIFS(Log!$F$2:$F$1000,A12)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="14">
+        <f>COUNTIFS(Log!$F$2:$F$1000,A13)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="14">
+        <f>COUNTIFS(Log!$F$2:$F$1000,A14)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B15" s="14">
+        <f>COUNTIFS(Log!$F$2:$F$1000,A15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A16" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="14">
+        <f>COUNTIFS(Log!$F$2:$F$1000,A16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="14">
+        <f>COUNTIFS(Log!$F$2:$F$1000,A17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="B22" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A22)</f>
+        <v>1</v>
+      </c>
+      <c r="C22" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A22,Log!$E$2:$E$1000,"Y")</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="15">
+        <f t="shared" ref="D22:D28" si="0">IFERROR(C22/B22,"—")</f>
+        <v>0</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="11">
-        <f>COUNTIFS(Log!$F$2:$F$999,A12)</f>
+      <c r="B23" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A23)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B13" s="11">
-        <f>COUNTIFS(Log!$F$2:$F$999,A13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="11">
-        <f>COUNTIFS(Log!$F$2:$F$999,A14)</f>
+      <c r="C23" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A23,Log!$E$2:$E$1000,"Y")</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="B15" s="11">
-        <f>COUNTIFS(Log!$F$2:$F$999,A15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="11">
-        <f>COUNTIFS(Log!$F$2:$F$999,A16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="11">
-        <f>COUNTIFS(Log!$F$2:$F$999,A17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A22)</f>
-        <v>0</v>
-      </c>
-      <c r="C22" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A22,Log!$E$2:$E$999,"Y")</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="12" t="str">
-        <f t="shared" ref="D22:D28" si="0">IFERROR(C22/B22,"—")</f>
-        <v>—</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A23)</f>
-        <v>1</v>
-      </c>
-      <c r="C23" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A23,Log!$E$2:$E$999,"Y")</f>
-        <v>1</v>
-      </c>
-      <c r="D23" s="12">
+      <c r="D23" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A24)</f>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A24)</f>
         <v>1</v>
       </c>
-      <c r="C24" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A24,Log!$E$2:$E$999,"Y")</f>
+      <c r="C24" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A24,Log!$E$2:$E$1000,"Y")</f>
         <v>1</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A25)</f>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B25" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A25)</f>
         <v>1</v>
       </c>
-      <c r="C25" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A25,Log!$E$2:$E$999,"Y")</f>
+      <c r="C25" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A25,Log!$E$2:$E$1000,"Y")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A26)</f>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B26" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A26)</f>
         <v>0</v>
       </c>
-      <c r="C26" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A26,Log!$E$2:$E$999,"Y")</f>
+      <c r="C26" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A26,Log!$E$2:$E$1000,"Y")</f>
         <v>0</v>
       </c>
-      <c r="D26" s="12" t="str">
+      <c r="D26" s="15" t="str">
         <f t="shared" si="0"/>
         <v>—</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A27)</f>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B27" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A27)</f>
         <v>0</v>
       </c>
-      <c r="C27" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A27,Log!$E$2:$E$999,"Y")</f>
+      <c r="C27" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A27,Log!$E$2:$E$1000,"Y")</f>
         <v>0</v>
       </c>
-      <c r="D27" s="12" t="str">
+      <c r="D27" s="15" t="str">
         <f t="shared" si="0"/>
         <v>—</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="B28" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A28)</f>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A28)</f>
         <v>0</v>
       </c>
-      <c r="C28" s="11">
-        <f>COUNTIFS(Log!$C$2:$C$999,A28,Log!$E$2:$E$999,"Y")</f>
+      <c r="C28" s="14">
+        <f>COUNTIFS(Log!$C$2:$C$1000,A28,Log!$E$2:$E$1000,"Y")</f>
         <v>0</v>
       </c>
-      <c r="D28" s="12" t="str">
+      <c r="D28" s="15" t="str">
         <f t="shared" si="0"/>
         <v>—</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="5" t="s">
-        <v>54</v>
-      </c>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="17">
+        <v>1</v>
+      </c>
+      <c r="B38" s="18">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=1,COUNTIFS(Log!$B$2:$B$2,"?*",Log!$E$2:$E$2,"Y")/1,NA())</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="17">
+        <v>2</v>
+      </c>
+      <c r="B39" s="18">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=2,COUNTIFS(Log!$B$2:$B$3,"?*",Log!$E$2:$E$3,"Y")/2,NA())</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="17">
+        <v>3</v>
+      </c>
+      <c r="B40" s="18">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=3,COUNTIFS(Log!$B$2:$B$4,"?*",Log!$E$2:$E$4,"Y")/3,NA())</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="G40" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="17">
+        <v>4</v>
+      </c>
+      <c r="B41" s="18">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=4,COUNTIFS(Log!$B$2:$B$5,"?*",Log!$E$2:$E$5,"Y")/4,NA())</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="17">
+        <v>5</v>
+      </c>
+      <c r="B42" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=5,COUNTIFS(Log!$B$2:$B$6,"?*",Log!$E$2:$E$6,"Y")/5,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="17">
+        <v>6</v>
+      </c>
+      <c r="B43" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=6,COUNTIFS(Log!$B$2:$B$7,"?*",Log!$E$2:$E$7,"Y")/6,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="17">
+        <v>7</v>
+      </c>
+      <c r="B44" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=7,COUNTIFS(Log!$B$2:$B$8,"?*",Log!$E$2:$E$8,"Y")/7,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="17">
+        <v>8</v>
+      </c>
+      <c r="B45" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=8,COUNTIFS(Log!$B$2:$B$9,"?*",Log!$E$2:$E$9,"Y")/8,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="17">
+        <v>9</v>
+      </c>
+      <c r="B46" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=9,COUNTIFS(Log!$B$2:$B$10,"?*",Log!$E$2:$E$10,"Y")/9,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="17">
+        <v>10</v>
+      </c>
+      <c r="B47" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=10,COUNTIFS(Log!$B$2:$B$11,"?*",Log!$E$2:$E$11,"Y")/10,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="17">
+        <v>11</v>
+      </c>
+      <c r="B48" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=11,COUNTIFS(Log!$B$2:$B$12,"?*",Log!$E$2:$E$12,"Y")/11,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A49" s="17">
+        <v>12</v>
+      </c>
+      <c r="B49" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=12,COUNTIFS(Log!$B$2:$B$13,"?*",Log!$E$2:$E$13,"Y")/12,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="17">
+        <v>13</v>
+      </c>
+      <c r="B50" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=13,COUNTIFS(Log!$B$2:$B$14,"?*",Log!$E$2:$E$14,"Y")/13,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" s="17">
+        <v>14</v>
+      </c>
+      <c r="B51" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=14,COUNTIFS(Log!$B$2:$B$15,"?*",Log!$E$2:$E$15,"Y")/14,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="17">
+        <v>15</v>
+      </c>
+      <c r="B52" s="18" t="e">
+        <f>IF(COUNTIF(Log!$B$2:$B$200,"?*")&gt;=15,COUNTIFS(Log!$B$2:$B$16,"?*",Log!$E$2:$E$16,"Y")/15,NA())</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="str">
+        <f>"Insights: "&amp;TEXT(SUM(B12:B13)/MAX(B5,1),"0%")&amp;" of corrections are Wrong Assumption or Missed Edge Case, pointing at spec clarity. Review the trend chart before concluding the agent itself is the problem."</f>
+        <v>Insights: 25% of corrections are Wrong Assumption or Missed Edge Case, pointing at spec clarity. Review the trend chart before concluding the agent itself is the problem.</v>
+      </c>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A58:J60"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1351,143 +2939,143 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="20" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
-        <v>55</v>
+      <c r="A1" s="19" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A2" s="14"/>
+      <c r="A2" s="17"/>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>56</v>
+      <c r="A3" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" s="14" t="s">
-        <v>57</v>
+      <c r="A4" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A5" s="14" t="s">
-        <v>58</v>
+      <c r="A5" s="17" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
-        <v>59</v>
+      <c r="A6" s="17" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
+      <c r="A7" s="17"/>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>60</v>
+      <c r="A8" s="7" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A9" s="14" t="s">
-        <v>61</v>
+      <c r="A9" s="17" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
-        <v>62</v>
+      <c r="A10" s="17" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
-        <v>63</v>
+      <c r="A11" s="17" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A12" s="14" t="s">
-        <v>64</v>
+      <c r="A12" s="17" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
+      <c r="A13" s="17"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
-        <v>65</v>
+      <c r="A14" s="7" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A15" s="14" t="s">
-        <v>66</v>
+      <c r="A15" s="17" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
-        <v>67</v>
+      <c r="A16" s="17" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A17" s="14" t="s">
-        <v>68</v>
+      <c r="A17" s="17" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
-        <v>69</v>
+      <c r="A18" s="17" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A19" s="14" t="s">
-        <v>70</v>
+      <c r="A19" s="17" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
+      <c r="A20" s="17"/>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
-        <v>71</v>
+      <c r="A21" s="7" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
-        <v>72</v>
+      <c r="A22" s="17" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A23" s="14" t="s">
-        <v>73</v>
+      <c r="A23" s="17" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A24" s="14" t="s">
-        <v>74</v>
+      <c r="A24" s="17" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A25" s="14"/>
+      <c r="A25" s="17"/>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>75</v>
+      <c r="A26" s="7" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A27" s="14" t="s">
-        <v>76</v>
+      <c r="A27" s="17" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A28" s="14" t="s">
-        <v>77</v>
+      <c r="A28" s="17" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A29" s="14" t="s">
-        <v>78</v>
+      <c r="A29" s="17" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
-        <v>79</v>
+      <c r="A30" s="17" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
